--- a/edim-ai-blueprint/docs/03_기능확인서_FVT/EDIM_기능확인서.xlsx
+++ b/edim-ai-blueprint/docs/03_기능확인서_FVT/EDIM_기능확인서.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="최종승인" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'기능확인항목'!$A$1:$K$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'기능확인항목'!$A$1:$K$180</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'비기능확인항목'!$A$1:$J$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -657,7 +657,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>기능 178건 · 비기능 22건</t>
+          <t>기능 179건 · 비기능 22건</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K179"/>
+  <dimension ref="A1:K180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1654,27 +1654,27 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>DOC-001</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>DOC 문서 관리</t>
+          <t>SYS-021</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>SYS 시스템 공통</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>문서 이력·Released Status</t>
+          <t>다국어 지원 (i18n)</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>문서별 Progress(Person/date/Released Status/Approver/App.Date/Version/DOC No.) 관리</t>
+          <t>UI 리소스 4로케일(KO/EN/JA/ZH) 번들, 데이터 라벨 번역(sys_translation), 로케일별 날짜·숫자·통화 포맷, 사용자·테넌트 기본 locale</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr"/>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>DOC-002</t>
+          <t>DOC-001</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -1699,12 +1699,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>관리 등급(보안 등급)</t>
+          <t>문서 이력·Released Status</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>문서 Management Grade(S-2 등) 설정 — 등급별 열람/출력 통제</t>
+          <t>문서별 Progress(Person/date/Released Status/Approver/App.Date/Version/DOC No.) 관리</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>DOC-003</t>
+          <t>DOC-002</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -1734,12 +1734,12 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Document Code 채번</t>
+          <t>관리 등급(보안 등급)</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>문서 코드 자동 생성 (예: EU-3-2020-450-6-21-4-SR-7)</t>
+          <t>문서 Management Grade(S-2 등) 설정 — 등급별 열람/출력 통제</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>DOC-004</t>
+          <t>DOC-003</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -1769,17 +1769,17 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>문서 보안 솔루션</t>
+          <t>Document Code 채번</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Authorization Settings·Security Solution 연계(워터마크·DRM·출력 통제)</t>
+          <t>문서 코드 자동 생성 (예: EU-3-2020-450-6-21-4-SR-7)</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr"/>
@@ -1794,27 +1794,27 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>CODE-001</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>CODE RCCS 코드 관리</t>
+          <t>DOC-004</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>DOC 문서 관리</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>코드 그룹 등록</t>
+          <t>문서 보안 솔루션</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Specification 그룹(KOF 등) 생성, Hierarchy 위치 지정</t>
+          <t>Authorization Settings·Security Solution 연계(워터마크·DRM·출력 통제)</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr"/>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>CODE-002</t>
+          <t>CODE-001</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>코드 자릿수 정의</t>
+          <t>코드 그룹 등록</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>그룹 내 Item Slot(A:Fan Model, B:Size…) 정의</t>
+          <t>Specification 그룹(KOF 등) 생성, Hierarchy 위치 지정</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>CODE-003</t>
+          <t>CODE-002</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>자릿수 값 등록</t>
+          <t>코드 자릿수 정의</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Sub Item List(350/400…, Gal./CU…) 등록</t>
+          <t>그룹 내 Item Slot(A:Fan Model, B:Size…) 정의</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>CODE-004</t>
+          <t>CODE-003</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Table 참조 값 연결</t>
+          <t>자릿수 값 등록</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>값이 Table 참조인 경우 tbl_data_table 연결</t>
+          <t>Sub Item List(350/400…, Gal./CU…) 등록</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>CODE-005</t>
+          <t>CODE-004</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>자재·일반구매품 코드 등록</t>
+          <t>Table 참조 값 연결</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Raw Material/GPI 그룹의 Sub Code 등록 (Motor 등)</t>
+          <t>값이 Table 참조인 경우 tbl_data_table 연결</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>CODE-006</t>
+          <t>CODE-005</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
@@ -1979,12 +1979,12 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Product Code 등록</t>
+          <t>자재·일반구매품 코드 등록</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Main Code(KDCR 3-13) 생성, 설명·Hierarchy 지정</t>
+          <t>Raw Material/GPI 그룹의 Sub Code 등록 (Motor 등)</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>CODE-007</t>
+          <t>CODE-006</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>Product Code 자릿수 구성</t>
+          <t>Product Code 등록</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>제품 코드가 사용할 Slot과 값 출처(Sub Code) 연결</t>
+          <t>Main Code(KDCR 3-13) 생성, 설명·Hierarchy 지정</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>CODE-008</t>
+          <t>CODE-007</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Code Relationship 설정</t>
+          <t>Product Code 자릿수 구성</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Mother-Child 관계 + 수량 + Slot 매핑 조건 등록</t>
+          <t>제품 코드가 사용할 Slot과 값 출처(Sub Code) 연결</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>CODE-009</t>
+          <t>CODE-008</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
@@ -2084,12 +2084,12 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Part List Running Test</t>
+          <t>Code Relationship 설정</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Mother 조합 선택 → 조건 일치 Child 전개 검증</t>
+          <t>Mother-Child 관계 + 수량 + Slot 매핑 조건 등록</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>CODE-010</t>
+          <t>CODE-009</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>BOM 전개</t>
+          <t>Part List Running Test</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>완성품 Code → Code Relationship 재귀 전개 → 전체 Part List</t>
+          <t>Mother 조합 선택 → 조건 일치 Child 전개 검증</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>CODE-011</t>
+          <t>CODE-010</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
@@ -2154,17 +2154,17 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Arrangement Code 등록</t>
+          <t>BOM 전개</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>표준 구성 조합(Double Deck 2 등) 등록</t>
+          <t>완성품 Code → Code Relationship 재귀 전개 → 전체 Part List</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr"/>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>CODE-012</t>
+          <t>CODE-011</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Arrangement 구성 설정</t>
+          <t>Arrangement Code 등록</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>구성 Module 배치·결합조건(Macro) 설정, DWG 연결</t>
+          <t>표준 구성 조합(Double Deck 2 등) 등록</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>CODE-013</t>
+          <t>CODE-012</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
@@ -2224,17 +2224,17 @@
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>코드 승인</t>
+          <t>Arrangement 구성 설정</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>코드 자산 승인 워크플로우 (Pending→Approved)</t>
+          <t>구성 Module 배치·결합조건(Macro) 설정, DWG 연결</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr"/>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>CODE-014</t>
+          <t>CODE-013</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>등록 Code Table 조회</t>
+          <t>코드 승인</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>그룹별 등록 코드 목록·상세·승인상태 조회</t>
+          <t>코드 자산 승인 워크플로우 (Pending→Approved)</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>CODE-015</t>
+          <t>CODE-014</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>코드 자산 연결</t>
+          <t>등록 Code Table 조회</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Sub/Product Code에 DWG(2D/3D)·Data Up-Load·Table 연결 관리</t>
+          <t>그룹별 등록 코드 목록·상세·승인상태 조회</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>CODE-016</t>
+          <t>CODE-015</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
@@ -2329,17 +2329,17 @@
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>코드 Excel Import/Export</t>
+          <t>코드 자산 연결</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Registered Code Table의 값 목록 Excel 일괄 등록/내보내기</t>
+          <t>Sub/Product Code에 DWG(2D/3D)·Data Up-Load·Table 연결 관리</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr"/>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>DWG-001</t>
-        </is>
-      </c>
-      <c r="C42" s="10" t="inlineStr">
-        <is>
-          <t>DWG 도면·PLM</t>
+          <t>CODE-016</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>CODE RCCS 코드 관리</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>도면 등록</t>
+          <t>코드 Excel Import/Export</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>도면 기본정보(도번·유형·축척·크기) 등록</t>
+          <t>Registered Code Table의 값 목록 Excel 일괄 등록/내보내기</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>DWG-002</t>
+          <t>DWG-001</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
@@ -2399,12 +2399,12 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>부품 호출·배치</t>
+          <t>도면 등록</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Hierarchy에서 하부 부품 도면 호출, Canvas Drag 배치</t>
+          <t>도면 기본정보(도번·유형·축척·크기) 등록</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>DWG-003</t>
+          <t>DWG-002</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>CAD 편집 명령</t>
+          <t>부품 호출·배치</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>복사/이동/반전/연장/삭제/회전, 좌표 이동, 색상·선형식</t>
+          <t>Hierarchy에서 하부 부품 도면 호출, Canvas Drag 배치</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>DWG-004</t>
+          <t>DWG-003</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>선택·스냅</t>
+          <t>CAD 편집 명령</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>1차 블록 선택, 2차 세부(끝점·중앙·모서리·중심) 선택</t>
+          <t>복사/이동/반전/연장/삭제/회전, 좌표 이동, 색상·선형식</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>DWG-005</t>
+          <t>DWG-004</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>치수선·지시선</t>
+          <t>선택·스냅</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>치수선 삽입, 지시선 자동 번호(A~N) 부여</t>
+          <t>1차 블록 선택, 2차 세부(끝점·중앙·모서리·중심) 선택</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>DWG-006</t>
+          <t>DWG-005</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -2539,12 +2539,12 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>치수 Macro 바인딩</t>
+          <t>치수선·지시선</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>치수마다 Macro 연결 또는 Variant 직접 입력</t>
+          <t>치수선 삽입, 지시선 자동 번호(A~N) 부여</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>DWG-007</t>
+          <t>DWG-006</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>치수·부품 동기화</t>
+          <t>치수 Macro 바인딩</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>입력 치수값에 의한 Parametric Design 반영</t>
+          <t>치수마다 Macro 연결 또는 Variant 직접 입력</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>DWG-008</t>
+          <t>DWG-007</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>설계·자료 우선순위</t>
+          <t>치수·부품 동기화</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Design/Data Priority 설정, 순환 참조 점검</t>
+          <t>입력 치수값에 의한 Parametric Design 반영</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>DWG-009</t>
+          <t>DWG-008</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>부품 상호관계 설정</t>
+          <t>설계·자료 우선순위</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Block A/B 선택, 조건1(수직·수평·중심)·조건2(접촉·좌표·각도), 관계값 Macro</t>
+          <t>Design/Data Priority 설정, 순환 참조 점검</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>DWG-010</t>
+          <t>DWG-009</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>설계 검증 규칙</t>
+          <t>부품 상호관계 설정</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>설계 조건 Macro 설정, 불일치 시 경고 문구</t>
+          <t>Block A/B 선택, 조건1(수직·수평·중심)·조건2(접촉·좌표·각도), 관계값 Macro</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>DWG-011</t>
+          <t>DWG-010</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>조립 순서 Set-up</t>
+          <t>설계 검증 규칙</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>조립품 부품에 조립 순서 번호·주의사항 정리</t>
+          <t>설계 조건 Macro 설정, 불일치 시 경고 문구</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>DWG-012</t>
+          <t>DWG-011</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Block 저장·호출</t>
+          <t>조립 순서 Set-up</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Block 단위 저장(임시저장→승인→사용), 상위 호출 시 Block 상태</t>
+          <t>조립품 부품에 조립 순서 번호·주의사항 정리</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>DWG-013</t>
+          <t>DWG-012</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
@@ -2784,12 +2784,12 @@
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>도면 개정 관리</t>
+          <t>Block 저장·호출</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Rev A/B/C 개정, 사유·내용 기록</t>
+          <t>Block 단위 저장(임시저장→승인→사용), 상위 호출 시 Block 상태</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>DWG-014</t>
+          <t>DWG-013</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
@@ -2819,12 +2819,12 @@
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>도면 승인</t>
+          <t>도면 개정 관리</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>작성→검토→승인→발행 단계 관리</t>
+          <t>Rev A/B/C 개정, 사유·내용 기록</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>DWG-015</t>
+          <t>DWG-014</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -2854,12 +2854,12 @@
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>도면 Import</t>
+          <t>도면 승인</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>DXF/DWG/PDF/STEP 업로드 → DrawingDocument 변환</t>
+          <t>작성→검토→승인→발행 단계 관리</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>DWG-016</t>
+          <t>DWG-015</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
@@ -2889,12 +2889,12 @@
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>도면 Export</t>
+          <t>도면 Import</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>DXF(R2010)/PDF 출력</t>
+          <t>DXF/DWG/PDF/STEP 업로드 → DrawingDocument 변환</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>DWG-017</t>
+          <t>DWG-016</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>부품 마스터</t>
+          <t>도면 Export</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>부품 등록(규격·재질·단위·단중·공급처·표준품)</t>
+          <t>DXF(R2010)/PDF 출력</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>DWG-018</t>
+          <t>DWG-017</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>재질 마스터</t>
+          <t>부품 마스터</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>재질 코드(SS400 등)·밀도·규격 관리</t>
+          <t>부품 등록(규격·재질·단위·단중·공급처·표준품)</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>DWG-019</t>
+          <t>DWG-018</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>도면 BOM 관리</t>
+          <t>재질 마스터</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>도면 부품 구성표(품번·수량·비고)</t>
+          <t>재질 코드(SS400 등)·밀도·규격 관리</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>DWG-020</t>
+          <t>DWG-019</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>첨부파일 관리</t>
+          <t>도면 BOM 관리</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>도면별 파일(DWG/PDF/STEP/PNG) 첨부</t>
+          <t>도면 부품 구성표(품번·수량·비고)</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>DWG-021</t>
+          <t>DWG-020</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -3064,17 +3064,17 @@
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>Work Process 공정 데이터</t>
+          <t>첨부파일 관리</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>Product Code별 자재/공정/조립 정보(작업장·인원·스킬·시간·창고·최소재고)</t>
+          <t>도면별 파일(DWG/PDF/STEP/PNG) 첨부</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr"/>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>DWG-022</t>
+          <t>DWG-021</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
@@ -3099,17 +3099,17 @@
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>도면 Templet 관리</t>
+          <t>Work Process 공정 데이터</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>설정 도면 Templet(도면 Frame·비율·형식) 등록·호출</t>
+          <t>Product Code별 자재/공정/조립 정보(작업장·인원·스킬·시간·창고·최소재고)</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr"/>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>DWG-023</t>
+          <t>DWG-022</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
@@ -3134,17 +3134,17 @@
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>CAD Mapping</t>
+          <t>도면 Templet 관리</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>도면 항목과 외부 CAD 파일(2D/3D) 매핑 연결</t>
+          <t>설정 도면 Templet(도면 Frame·비율·형식) 등록·호출</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr"/>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>DWG-024</t>
+          <t>DWG-023</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
@@ -3169,17 +3169,17 @@
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>설계 Simulation</t>
+          <t>CAD Mapping</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>설정된 관계·검증 규칙 기반 도면 동작 시뮬레이션(우측 판넬)</t>
+          <t>도면 항목과 외부 CAD 파일(2D/3D) 매핑 연결</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr"/>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>DWG-025</t>
+          <t>DWG-024</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
@@ -3204,17 +3204,17 @@
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>측정·특성 도구</t>
+          <t>설계 Simulation</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>치수 측정(수평/수직/정렬/각도/호길이/면적/무게), 특성 변경(색상/투명도/선굵기/레이어), 자르기(Trim), 그룹화/해제, 등각·단면 View</t>
+          <t>설정된 관계·검증 규칙 기반 도면 동작 시뮬레이션(우측 판넬)</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr"/>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>DWG-026</t>
+          <t>DWG-025</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
@@ -3239,17 +3239,17 @@
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Referencers 역참조 조회</t>
+          <t>측정·특성 도구</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>도면/부품의 Where-used — 어느 상위 도면·Arrangement에서 참조되는지 조회</t>
+          <t>치수 측정(수평/수직/정렬/각도/호길이/면적/무게), 특성 변경(색상/투명도/선굵기/레이어), 자르기(Trim), 그룹화/해제, 등각·단면 View</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr"/>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>DWG-027</t>
+          <t>DWG-026</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>Variants·Supersedure 관리</t>
+          <t>Referencers 역참조 조회</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>도면 변형(Variants) 목록과 대체 관계(Supersedure — 신규정이 구버전 대체) 관리</t>
+          <t>도면/부품의 Where-used — 어느 상위 도면·Arrangement에서 참조되는지 조회</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
@@ -3299,27 +3299,27 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>TBL-001</t>
-        </is>
-      </c>
-      <c r="C69" s="11" t="inlineStr">
-        <is>
-          <t>TBL 데이터 Table</t>
+          <t>DWG-027</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>DWG 도면·PLM</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Table 정의</t>
+          <t>Variants·Supersedure 관리</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>Variant/Tech/Material Table 생성(열 정의·부서·Hierarchy 주소)</t>
+          <t>도면 변형(Variants) 목록과 대체 관계(Supersedure — 신규정이 구버전 대체) 관리</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr"/>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>TBL-002</t>
+          <t>TBL-001</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
@@ -3344,12 +3344,12 @@
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>Table 행 편집</t>
+          <t>Table 정의</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>행 추가/편집/일괄 입력 (Key + A~N 값)</t>
+          <t>Variant/Tech/Material Table 생성(열 정의·부서·Hierarchy 주소)</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>TBL-003</t>
+          <t>TBL-002</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Excel Import</t>
+          <t>Table 행 편집</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>정해진 양식의 Excel에서 Table 행 일괄 등록</t>
+          <t>행 추가/편집/일괄 입력 (Key + A~N 값)</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>TBL-004</t>
+          <t>TBL-003</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>Table 범위 조회</t>
+          <t>Excel Import</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Macro 참조용 범위 조회 API(TableN(col,range))</t>
+          <t>정해진 양식의 Excel에서 Table 행 일괄 등록</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>TBL-005</t>
+          <t>TBL-004</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
@@ -3449,17 +3449,17 @@
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Data Up-Load</t>
+          <t>Table 범위 조회</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>Data/File/Image 자료 등록(부서·유형·이름·설명)</t>
+          <t>Macro 참조용 범위 조회 API(TableN(col,range))</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr"/>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>TBL-006</t>
+          <t>TBL-005</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
@@ -3484,17 +3484,17 @@
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>Table 승인</t>
+          <t>Data Up-Load</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>Table 정의·대량 변경 승인</t>
+          <t>Data/File/Image 자료 등록(부서·유형·이름·설명)</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr"/>
@@ -3509,27 +3509,27 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>TBX-001</t>
-        </is>
-      </c>
-      <c r="C75" s="12" t="inlineStr">
-        <is>
-          <t>TBX Toolbox</t>
+          <t>TBL-006</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>TBL 데이터 Table</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>UI Designer 위젯 배치</t>
+          <t>Table 승인</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>Widget Palette(Button/Label/Entry/Text/Canvas/Frame/Menu/Combo/Table) Drag&amp;Drop</t>
+          <t>Table 정의·대량 변경 승인</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr"/>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>TBX-002</t>
+          <t>TBX-001</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>동작 Templet 바인딩</t>
+          <t>UI Designer 위젯 배치</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>위젯별 동작(저장/삭제/복사/등록/찾기)·대상 Data 연결</t>
+          <t>Widget Palette(Button/Label/Entry/Text/Canvas/Frame/Menu/Combo/Table) Drag&amp;Drop</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>TBX-003</t>
+          <t>TBX-002</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Form 저장·버전·게시</t>
+          <t>동작 Templet 바인딩</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>layout_def 저장, 버전 관리, 승인 후 게시</t>
+          <t>위젯별 동작(저장/삭제/복사/등록/찾기)·대상 Data 연결</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>TBX-004</t>
+          <t>TBX-003</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>AI UI 제안</t>
+          <t>Form 저장·버전·게시</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>Application 설명 입력 → 용도/항목/필요 DB Table 정리된 UI 초안</t>
+          <t>layout_def 저장, 버전 관리, 승인 후 게시</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>TBX-005</t>
+          <t>TBX-004</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Prompt 입력</t>
+          <t>AI UI 제안</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>자연어로 계산 요구 기술</t>
+          <t>Application 설명 입력 → 용도/항목/필요 DB Table 정리된 UI 초안</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>TBX-006</t>
+          <t>TBX-005</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
@@ -3694,17 +3694,17 @@
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>Macro 수식 편집</t>
+          <t>Prompt 입력</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>Excel 문법 계산식 작성(TableN/Var/PreC 참조)</t>
+          <t>자연어로 계산 요구 기술</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>TBX-007</t>
+          <t>TBX-006</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
@@ -3729,17 +3729,17 @@
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Flowchart 편집</t>
+          <t>Macro 수식 편집</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>흐름도 기반 로직 편집</t>
+          <t>Excel 문법 계산식 작성(TableN/Var/PreC 참조)</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr"/>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>TBX-008</t>
+          <t>TBX-007</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>4-Way Sync 변환</t>
+          <t>Flowchart 편집</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>Prompt↔Macro↔Flowchart↔Coding 실시간 상호 변환</t>
+          <t>흐름도 기반 로직 편집</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>TBX-009</t>
+          <t>TBX-008</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
@@ -3799,12 +3799,12 @@
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>함수·그래프 마법사</t>
+          <t>4-Way Sync 변환</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>함수 검색/설명/삽입, 그래프 유형 선택 마법사</t>
+          <t>Prompt↔Macro↔Flowchart↔Coding 실시간 상호 변환</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>TBX-010</t>
+          <t>TBX-009</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>Data Information Call</t>
+          <t>함수·그래프 마법사</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>Enterprise DB(Table/Chart/Formula) 탐색·주소 지정</t>
+          <t>함수 검색/설명/삽입, 그래프 유형 선택 마법사</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>TBX-011</t>
+          <t>TBX-010</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
@@ -3869,17 +3869,17 @@
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Macro Test Run</t>
+          <t>Data Information Call</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>조건값 입력 → 계산 실행 → 결과 확인</t>
+          <t>Enterprise DB(Table/Chart/Formula) 탐색·주소 지정</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr"/>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>TBX-012</t>
+          <t>TBX-011</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
@@ -3904,12 +3904,12 @@
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>Macro 승인·버전</t>
+          <t>Macro Test Run</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>생성/편집/삭제의 엄격한 검증·승인 절차, 버전 관리</t>
+          <t>조건값 입력 → 계산 실행 → 결과 확인</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>TBX-013</t>
+          <t>TBX-012</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
@@ -3939,17 +3939,17 @@
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Templet 관리</t>
+          <t>Macro 승인·버전</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>Command button/Combo/Data Table/Print/Graph Templet 등록·재사용</t>
+          <t>생성/편집/삭제의 엄격한 검증·승인 절차, 버전 관리</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr"/>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>TBX-014</t>
+          <t>TBX-013</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>기능 찾기·도움말</t>
+          <t>Templet 관리</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>자연어로 필요 기능/함수 검색(기능 찾기), User Help·Manual 연동</t>
+          <t>Command button/Combo/Data Table/Print/Graph Templet 등록·재사용</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>TBX-015</t>
+          <t>TBX-014</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
@@ -4009,17 +4009,17 @@
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>인터넷 검색·AI 질의</t>
+          <t>기능 찾기·도움말</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>Toolbox 내 인터넷 검색 기능, AI 질의응답(내부 자료 검색·응답)</t>
+          <t>자연어로 필요 기능/함수 검색(기능 찾기), User Help·Manual 연동</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr"/>
@@ -4034,27 +4034,27 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>CPQ-001</t>
-        </is>
-      </c>
-      <c r="C90" s="13" t="inlineStr">
-        <is>
-          <t>CPQ CPQ 제품선정</t>
+          <t>TBX-015</t>
+        </is>
+      </c>
+      <c r="C90" s="12" t="inlineStr">
+        <is>
+          <t>TBX Toolbox</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>제품 선정 화면</t>
+          <t>인터넷 검색·AI 질의</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>Product Tree에서 제품 선택, Selection 시작</t>
+          <t>Toolbox 내 인터넷 검색 기능, AI 질의응답(내부 자료 검색·응답)</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr"/>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>CPQ-002</t>
+          <t>CPQ-001</t>
         </is>
       </c>
       <c r="C91" s="13" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Arrangement 구성</t>
+          <t>제품 선정 화면</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>모듈 이미지 Drag 조합, 이동/삭제/분할/통합, 치수 DB 표시</t>
+          <t>Product Tree에서 제품 선택, Selection 시작</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>CPQ-003</t>
+          <t>CPQ-002</t>
         </is>
       </c>
       <c r="C92" s="13" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>사양 입력</t>
+          <t>Arrangement 구성</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>Spec List 입력 Table(풍량·정압·온도 등)</t>
+          <t>모듈 이미지 Drag 조합, 이동/삭제/분할/통합, 치수 DB 표시</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>CPQ-004</t>
+          <t>CPQ-003</t>
         </is>
       </c>
       <c r="C93" s="13" t="inlineStr">
@@ -4149,17 +4149,17 @@
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>고객 사양 Excel Import</t>
+          <t>사양 입력</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>정해진 Excel 양식 Import → Selection 입력 항 자동 적용</t>
+          <t>Spec List 입력 Table(풍량·정압·온도 등)</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr"/>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>CPQ-005</t>
+          <t>CPQ-004</t>
         </is>
       </c>
       <c r="C94" s="13" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>기술 데이터 화면</t>
+          <t>고객 사양 Excel Import</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>Fan 선정 상세(Impeller/Motor/Casing 옵션), 성능 곡선, 기술 Table</t>
+          <t>정해진 Excel 양식 Import → Selection 입력 항 자동 적용</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>CPQ-006</t>
+          <t>CPQ-005</t>
         </is>
       </c>
       <c r="C95" s="13" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>Document Template</t>
+          <t>기술 데이터 화면</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>입력값(온도·습도)→Macro 계산→출력값(밀도), 그래프 표시</t>
+          <t>Fan 선정 상세(Impeller/Motor/Casing 옵션), 성능 곡선, 기술 Table</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>CPQ-007</t>
+          <t>CPQ-006</t>
         </is>
       </c>
       <c r="C96" s="13" t="inlineStr">
@@ -4254,17 +4254,17 @@
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>완성품 Code 생성</t>
+          <t>Document Template</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>Slot 선택 조합 → Finished Goods Code 확정</t>
+          <t>입력값(온도·습도)→Macro 계산→출력값(밀도), 그래프 표시</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr"/>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>CPQ-008</t>
+          <t>CPQ-007</t>
         </is>
       </c>
       <c r="C97" s="13" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>Sub Item List 조회</t>
+          <t>완성품 Code 생성</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>완성품 Code 연결 하위 Code 전개 목록, Click 시 세부 정보</t>
+          <t>Slot 선택 조합 → Finished Goods Code 확정</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>CPQ-009</t>
+          <t>CPQ-008</t>
         </is>
       </c>
       <c r="C98" s="13" t="inlineStr">
@@ -4324,17 +4324,17 @@
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>X-Code 비규격 처리</t>
+          <t>Sub Item List 조회</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>비표준 Option 선택 시 X-Code 표시→검토요청→R&amp;D 신규설계→신규코드 등록→복귀</t>
+          <t>완성품 Code 연결 하위 Code 전개 목록, Click 시 세부 정보</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr"/>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>CPQ-010</t>
+          <t>CPQ-009</t>
         </is>
       </c>
       <c r="C99" s="13" t="inlineStr">
@@ -4359,17 +4359,17 @@
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>DWG View</t>
+          <t>X-Code 비규격 처리</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>선정 제품 도면 확인, 3각법 6면·전체 View</t>
+          <t>비표준 Option 선택 시 X-Code 표시→검토요청→R&amp;D 신규설계→신규코드 등록→복귀</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr"/>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>CPQ-011</t>
+          <t>CPQ-010</t>
         </is>
       </c>
       <c r="C100" s="13" t="inlineStr">
@@ -4394,17 +4394,17 @@
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>Selection Set-up</t>
+          <t>DWG View</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>선정 UI 구성 — Product Tree 가져오기, Item Image·Arrangement 정의</t>
+          <t>선정 제품 도면 확인, 3각법 6면·전체 View</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr"/>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>CPQ-012</t>
+          <t>CPQ-011</t>
         </is>
       </c>
       <c r="C101" s="13" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>Technical·Document Set-up</t>
+          <t>Selection Set-up</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>기술 Data/서류 Form 구성(입출력 항목·그래프 Templet)</t>
+          <t>선정 UI 구성 — Product Tree 가져오기, Item Image·Arrangement 정의</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>CPQ-013</t>
+          <t>CPQ-012</t>
         </is>
       </c>
       <c r="C102" s="13" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>Print Set-up</t>
+          <t>Technical·Document Set-up</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>양식 배치·Data 위치·그래프·워터마크·Font·용지·머리글/바닥글·내보내기(PDF/Office)</t>
+          <t>기술 Data/서류 Form 구성(입출력 항목·그래프 Templet)</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>CPQ-014</t>
+          <t>CPQ-013</t>
         </is>
       </c>
       <c r="C103" s="13" t="inlineStr">
@@ -4499,12 +4499,12 @@
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>Selection Toolbar 구성</t>
+          <t>Print Set-up</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>사용자 명령 버튼 Templet 제작 — Arrangement/Move/Delete/Add/Copy/DWG View, 사양 입력 Combo, 정형화 사양 호출(Excel), 도구 이미지 설정</t>
+          <t>양식 배치·Data 위치·그래프·워터마크·Font·용지·머리글/바닥글·내보내기(PDF/Office)</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>CPQ-015</t>
+          <t>CPQ-014</t>
         </is>
       </c>
       <c r="C104" s="13" t="inlineStr">
@@ -4534,12 +4534,12 @@
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>Module 이미지 제작</t>
+          <t>Selection Toolbar 구성</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>제품 구성용 Module 그림 제작 도구(그림 제작 Modul) — 저장 이미지 호출·제어</t>
+          <t>사용자 명령 버튼 Templet 제작 — Arrangement/Move/Delete/Add/Copy/DWG View, 사양 입력 Combo, 정형화 사양 호출(Excel), 도구 이미지 설정</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
@@ -4559,27 +4559,27 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>RUN-001</t>
-        </is>
-      </c>
-      <c r="C105" s="14" t="inlineStr">
-        <is>
-          <t>RUN EDIM Run</t>
+          <t>CPQ-015</t>
+        </is>
+      </c>
+      <c r="C105" s="13" t="inlineStr">
+        <is>
+          <t>CPQ CPQ 제품선정</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>Run 실행 요청</t>
+          <t>Module 이미지 제작</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>Selection에서 BOM/DWG/PRICING/TECH/ALL 실행</t>
+          <t>제품 구성용 Module 그림 제작 도구(그림 제작 Modul) — 저장 이미지 호출·제어</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr"/>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>RUN-002</t>
+          <t>RUN-001</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
@@ -4604,12 +4604,12 @@
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>BOM·Part List 생성</t>
+          <t>Run 실행 요청</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>Main Code 시작 Code Relationship 전개 → BOM 저장</t>
+          <t>Selection에서 BOM/DWG/PRICING/TECH/ALL 실행</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>RUN-003</t>
+          <t>RUN-002</t>
         </is>
       </c>
       <c r="C107" s="14" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>치수 Macro 일괄 실행</t>
+          <t>BOM·Part List 생성</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>Sub-code 조건별 Macro 계산 → 계산값 Table 생성·저장</t>
+          <t>Main Code 시작 Code Relationship 전개 → BOM 저장</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>RUN-004</t>
+          <t>RUN-003</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>승인도면 생성</t>
+          <t>치수 Macro 일괄 실행</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>CPQ Main Concept Drawing → 승인도면(CAD, 필요시 PDF)</t>
+          <t>Sub-code 조건별 Macro 계산 → 계산값 Table 생성·저장</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>RUN-005</t>
+          <t>RUN-004</t>
         </is>
       </c>
       <c r="C109" s="14" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>제작도면 생성</t>
+          <t>승인도면 생성</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>각 Code 연결 도면의 Macro Run → 치수 반영 도면 추출</t>
+          <t>CPQ Main Concept Drawing → 승인도면(CAD, 필요시 PDF)</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>RUN-006</t>
+          <t>RUN-005</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
@@ -4744,17 +4744,17 @@
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>기술자료 계산·생성</t>
+          <t>제작도면 생성</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>Technical Data Calculation → Project Data folder 저장</t>
+          <t>각 Code 연결 도면의 Macro Run → 치수 반영 도면 추출</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr"/>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>RUN-007</t>
+          <t>RUN-006</t>
         </is>
       </c>
       <c r="C111" s="14" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>일반 서류 생성</t>
+          <t>기술자료 계산·생성</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>General Document — 각 Code 연결 서류 계산·생성</t>
+          <t>Technical Data Calculation → Project Data folder 저장</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>RUN-008</t>
+          <t>RUN-007</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
@@ -4814,17 +4814,17 @@
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>Run 상태·오류 조회</t>
+          <t>일반 서류 생성</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>진행률·단계별 상태·Macro 오류/검증 경고 목록</t>
+          <t>General Document — 각 Code 연결 서류 계산·생성</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr"/>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>RUN-009</t>
+          <t>RUN-008</t>
         </is>
       </c>
       <c r="C113" s="14" t="inlineStr">
@@ -4849,12 +4849,12 @@
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>산출물 조회</t>
+          <t>Run 상태·오류 조회</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>Project Folder(DWG/Price/Data/BOM)별 산출물 목록·다운로드</t>
+          <t>진행률·단계별 상태·Macro 오류/검증 경고 목록</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>RUN-010</t>
+          <t>RUN-009</t>
         </is>
       </c>
       <c r="C114" s="14" t="inlineStr">
@@ -4884,12 +4884,12 @@
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>BOM Export·부분 Run</t>
+          <t>산출물 조회</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>BOM 화면의 EBOM Run(BOM만)/EDIM Run(전체)/Export(Excel) 구분 실행</t>
+          <t>Project Folder(DWG/Price/Data/BOM)별 산출물 목록·다운로드</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
@@ -4909,27 +4909,27 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>CST-001</t>
-        </is>
-      </c>
-      <c r="C115" s="15" t="inlineStr">
-        <is>
-          <t>CST 원가·견적</t>
+          <t>RUN-010</t>
+        </is>
+      </c>
+      <c r="C115" s="14" t="inlineStr">
+        <is>
+          <t>RUN EDIM Run</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>단가 관리</t>
+          <t>BOM Export·부분 Run</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>견적/구매이력/재고단가/견적적용 4종 단가 Table</t>
+          <t>BOM 화면의 EBOM Run(BOM만)/EDIM Run(전체)/Export(Excel) 구분 실행</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr"/>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>CST-002</t>
+          <t>CST-001</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>자재비 계산</t>
+          <t>단가 관리</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>원자재 정보(면적·무게·부피)×단가 → Material Cost</t>
+          <t>견적/구매이력/재고단가/견적적용 4종 단가 Table</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>CST-003</t>
+          <t>CST-002</t>
         </is>
       </c>
       <c r="C117" s="15" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>제조비 계산</t>
+          <t>자재비 계산</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>Work Process 제조 정보(시간·임율·장비) → Manufacturing Cost</t>
+          <t>원자재 정보(면적·무게·부피)×단가 → Material Cost</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>CST-004</t>
+          <t>CST-003</t>
         </is>
       </c>
       <c r="C118" s="15" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>직접비 집계</t>
+          <t>제조비 계산</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>자재비+제조비+기타 직접비 → Direct Cost</t>
+          <t>Work Process 제조 정보(시간·임율·장비) → Manufacturing Cost</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>CST-005</t>
+          <t>CST-004</t>
         </is>
       </c>
       <c r="C119" s="15" t="inlineStr">
@@ -5059,12 +5059,12 @@
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>PCR 작성</t>
+          <t>직접비 집계</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>Business Type별 원가 전개(조달·외주·판관비)→ EBIT</t>
+          <t>자재비+제조비+기타 직접비 → Direct Cost</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>CST-006</t>
+          <t>CST-005</t>
         </is>
       </c>
       <c r="C120" s="15" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>견적서 생성·출력</t>
+          <t>PCR 작성</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>PCR 기반 견적서(수량·단가·조건) 생성, PDF 출력</t>
+          <t>Business Type별 원가 전개(조달·외주·판관비)→ EBIT</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>CST-007</t>
+          <t>CST-006</t>
         </is>
       </c>
       <c r="C121" s="15" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>견적 이력 관리</t>
+          <t>견적서 생성·출력</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>견적 상태(DRAFT/SENT/ORDERED) 및 이력</t>
+          <t>PCR 기반 견적서(수량·단가·조건) 생성, PDF 출력</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
@@ -5154,27 +5154,27 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>ERP-001</t>
-        </is>
-      </c>
-      <c r="C122" s="16" t="inlineStr">
-        <is>
-          <t>ERP ERP 업무</t>
+          <t>CST-007</t>
+        </is>
+      </c>
+      <c r="C122" s="15" t="inlineStr">
+        <is>
+          <t>CST 원가·견적</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>프로젝트 등록</t>
+          <t>견적 이력 관리</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>Project No 자동, 영업단계(기술제안~종료), Client·담당자·Pain Point·접수자료</t>
+          <t>견적 상태(DRAFT/SENT/ORDERED) 및 이력</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr"/>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>ERP-002</t>
+          <t>ERP-001</t>
         </is>
       </c>
       <c r="C123" s="16" t="inlineStr">
@@ -5199,17 +5199,17 @@
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>프로세스 이벤트 관리</t>
+          <t>프로젝트 등록</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>프로세스 코드별 이벤트 생성·상태 전이(TODO→진행→완료)</t>
+          <t>Project No 자동, 영업단계(기술제안~종료), Client·담당자·Pain Point·접수자료</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr"/>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>ERP-003</t>
+          <t>ERP-002</t>
         </is>
       </c>
       <c r="C124" s="16" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>부서별 업무함</t>
+          <t>프로세스 이벤트 관리</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>부서·담당자별 To-do/진행/완료 목록</t>
+          <t>프로세스 코드별 이벤트 생성·상태 전이(TODO→진행→완료)</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>ERP-004</t>
+          <t>ERP-003</t>
         </is>
       </c>
       <c r="C125" s="16" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>영업 프로세스</t>
+          <t>부서별 업무함</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>견적검토(PCR)→견적(QCR)→수주(OR) 흐름 처리</t>
+          <t>부서·담당자별 To-do/진행/완료 목록</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>ERP-005</t>
+          <t>ERP-004</t>
         </is>
       </c>
       <c r="C126" s="16" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>승인도서·고객승인</t>
+          <t>영업 프로세스</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>AP 생성→APP 고객 승인 처리</t>
+          <t>견적검토(PCR)→견적(QCR)→수주(OR) 흐름 처리</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>ERP-006</t>
+          <t>ERP-005</t>
         </is>
       </c>
       <c r="C127" s="16" t="inlineStr">
@@ -5339,12 +5339,12 @@
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>제작 프로세스</t>
+          <t>승인도서·고객승인</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>제작의뢰(MR)→제작점검(MRR)→Part List(PL)→BOM</t>
+          <t>AP 생성→APP 고객 승인 처리</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>ERP-007</t>
+          <t>ERP-006</t>
         </is>
       </c>
       <c r="C128" s="16" t="inlineStr">
@@ -5374,12 +5374,12 @@
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>자재 프로세스</t>
+          <t>제작 프로세스</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>발주요청(PR)→발주(PO)→입고(MI)→출고(MO)→수령(RM)→검사(ER)</t>
+          <t>제작의뢰(MR)→제작점검(MRR)→Part List(PL)→BOM</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>ERP-008</t>
+          <t>ERP-007</t>
         </is>
       </c>
       <c r="C129" s="16" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>생산 프로세스</t>
+          <t>자재 프로세스</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>생산계획(MP)→작업지시(WR)→입고(SFI)→검사(EF)→완료(FF), Stock 생산(SPP)</t>
+          <t>발주요청(PR)→발주(PO)→입고(MI)→출고(MO)→수령(RM)→검사(ER)</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>ERP-009</t>
+          <t>ERP-008</t>
         </is>
       </c>
       <c r="C130" s="16" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>출고·납품 프로세스</t>
+          <t>생산 프로세스</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>출고요청(FDR)→고객출고(SFO)→납품(DF)→기성청구(IR)</t>
+          <t>생산계획(MP)→작업지시(WR)→입고(SFI)→검사(EF)→완료(FF), Stock 생산(SPP)</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>ERP-010</t>
+          <t>ERP-009</t>
         </is>
       </c>
       <c r="C131" s="16" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>시운전·CS</t>
+          <t>출고·납품 프로세스</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>시운전 요청(CR)→시운전(CF), 인증서 발급</t>
+          <t>출고요청(FDR)→고객출고(SFO)→납품(DF)→기성청구(IR)</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>ERP-011</t>
+          <t>ERP-010</t>
         </is>
       </c>
       <c r="C132" s="16" t="inlineStr">
@@ -5514,12 +5514,12 @@
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>재무 프로세스</t>
+          <t>시운전·CS</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>세금계산 매입/매출(II/IO), 출금/입금(PA/PI), 정산(RR/RA), 재무관리(FM)</t>
+          <t>시운전 요청(CR)→시운전(CF), 인증서 발급</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>ERP-012</t>
+          <t>ERP-011</t>
         </is>
       </c>
       <c r="C133" s="16" t="inlineStr">
@@ -5549,12 +5549,12 @@
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>부적합 처리</t>
+          <t>재무 프로세스</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>NCF 요청·처리, 재작업 요청(WR)</t>
+          <t>세금계산 매입/매출(II/IO), 출금/입금(PA/PI), 정산(RR/RA), 재무관리(FM)</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>ERP-013</t>
+          <t>ERP-012</t>
         </is>
       </c>
       <c r="C134" s="16" t="inlineStr">
@@ -5584,12 +5584,12 @@
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>평가</t>
+          <t>부적합 처리</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>업체 평가(CE), Project 평가(PE)</t>
+          <t>NCF 요청·처리, 재작업 요청(WR)</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>ERP-014</t>
+          <t>ERP-013</t>
         </is>
       </c>
       <c r="C135" s="16" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>평가</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>전후 공정·Project 일정·Event 상황·이상 경고(시간/자금)·손익·자금 흐름</t>
+          <t>업체 평가(CE), Project 평가(PE)</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>ERP-015</t>
+          <t>ERP-014</t>
         </is>
       </c>
       <c r="C136" s="16" t="inlineStr">
@@ -5654,17 +5654,17 @@
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>회사 마스터</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
         <is>
-          <t>고객/공급/파트너/은행 등록, 담당자, 평가등급, 지불조건</t>
+          <t>전후 공정·Project 일정·Event 상황·이상 경고(시간/자금)·손익·자금 흐름</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr"/>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>ERP-016</t>
+          <t>ERP-015</t>
         </is>
       </c>
       <c r="C137" s="16" t="inlineStr">
@@ -5689,17 +5689,17 @@
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>사용자 정의 ERP Toolbar</t>
+          <t>회사 마스터</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>ERP Toolbar 항목 사용자 편집, 권한별 표시</t>
+          <t>고객/공급/파트너/은행 등록, 담당자, 평가등급, 지불조건</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr"/>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>ERP-017</t>
+          <t>ERP-016</t>
         </is>
       </c>
       <c r="C138" s="16" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>구매 조건 관리</t>
+          <t>사용자 정의 ERP Toolbar</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>공급처(국가/본사)·납기·납품조건(EXW/FOB/CIP, 설치/상차/하차)·운송(트럭/배/항공)·지불조건·화폐·물품형식(물건/서비스/인력/협력사)·최소구매수량·인증서·단위(부피/체적/면적/수량)</t>
+          <t>ERP Toolbar 항목 사용자 편집, 권한별 표시</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>ERP-018</t>
+          <t>ERP-017</t>
         </is>
       </c>
       <c r="C139" s="16" t="inlineStr">
@@ -5759,12 +5759,12 @@
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>제품코드 매핑</t>
+          <t>구매 조건 관리</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>사용자용 코드 ↔ 공급자용 코드 매핑 관리</t>
+          <t>공급처(국가/본사)·납기·납품조건(EXW/FOB/CIP, 설치/상차/하차)·운송(트럭/배/항공)·지불조건·화폐·물품형식(물건/서비스/인력/협력사)·최소구매수량·인증서·단위(부피/체적/면적/수량)</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>ERP-019</t>
+          <t>ERP-018</t>
         </is>
       </c>
       <c r="C140" s="16" t="inlineStr">
@@ -5794,12 +5794,12 @@
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>재고 관리</t>
+          <t>제품코드 매핑</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>적정 재고량, 유통기한 관리</t>
+          <t>사용자용 코드 ↔ 공급자용 코드 매핑 관리</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>ERP-020</t>
+          <t>ERP-019</t>
         </is>
       </c>
       <c r="C141" s="16" t="inlineStr">
@@ -5829,12 +5829,12 @@
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>창고 관리</t>
+          <t>재고 관리</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>자재 분류(원자재/가공/구매), 물성 위험등급(액체-독극물/가스-폭발성/고체-판·파이프·개), 저장위치 계층(지역/공장/창고/Storage/Sector), 보관품질(정기점검·유통기한), 입출고 통제·기록</t>
+          <t>적정 재고량, 유통기한 관리</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>ERP-021</t>
+          <t>ERP-020</t>
         </is>
       </c>
       <c r="C142" s="16" t="inlineStr">
@@ -5864,12 +5864,12 @@
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>재고 단가 관리</t>
+          <t>창고 관리</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
         <is>
-          <t>재고 단가 4종 산출 — 최고/최저/평균/최근</t>
+          <t>자재 분류(원자재/가공/구매), 물성 위험등급(액체-독극물/가스-폭발성/고체-판·파이프·개), 저장위치 계층(지역/공장/창고/Storage/Sector), 보관품질(정기점검·유통기한), 입출고 통제·기록</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>ERP-022</t>
+          <t>ERP-021</t>
         </is>
       </c>
       <c r="C143" s="16" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="D143" s="6" t="inlineStr">
         <is>
-          <t>MRP 자재 소요 계획</t>
+          <t>재고 단가 관리</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>제품 단위당 BOM 기반 자재 소요량·소요 시기 산출</t>
+          <t>재고 단가 4종 산출 — 최고/최저/평균/최근</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>ERP-023</t>
+          <t>ERP-022</t>
         </is>
       </c>
       <c r="C144" s="16" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="D144" s="6" t="inlineStr">
         <is>
-          <t>생산 Scheduling·Capacity</t>
+          <t>MRP 자재 소요 계획</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
         <is>
-          <t>주문량·가용 자원 기반 생산 일정, 생산능력(Capacity Planning) 분석</t>
+          <t>제품 단위당 BOM 기반 자재 소요량·소요 시기 산출</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>ERP-024</t>
+          <t>ERP-023</t>
         </is>
       </c>
       <c r="C145" s="16" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="D145" s="6" t="inlineStr">
         <is>
-          <t>작업지시 관리</t>
+          <t>생산 Scheduling·Capacity</t>
         </is>
       </c>
       <c r="E145" s="6" t="inlineStr">
         <is>
-          <t>작업 지시서(양식) 발행, 작업 단계별 진행 상황 기록·모니터링</t>
+          <t>주문량·가용 자원 기반 생산 일정, 생산능력(Capacity Planning) 분석</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>ERP-025</t>
+          <t>ERP-024</t>
         </is>
       </c>
       <c r="C146" s="16" t="inlineStr">
@@ -6004,12 +6004,12 @@
       </c>
       <c r="D146" s="6" t="inlineStr">
         <is>
-          <t>공정 관리</t>
+          <t>작업지시 관리</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
         <is>
-          <t>공정별 데이터 실시간 수집·분석 — 작업장/기계종류/작업인원/필요스킬등급/작업시간/조립공정/전·후공정 DB</t>
+          <t>작업 지시서(양식) 발행, 작업 단계별 진행 상황 기록·모니터링</t>
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>ERP-026</t>
+          <t>ERP-025</t>
         </is>
       </c>
       <c r="C147" s="16" t="inlineStr">
@@ -6039,12 +6039,12 @@
       </c>
       <c r="D147" s="6" t="inlineStr">
         <is>
-          <t>자재흐름·물류 관리</t>
+          <t>공정 관리</t>
         </is>
       </c>
       <c r="E147" s="6" t="inlineStr">
         <is>
-          <t>물류 창고, 물류 방식 관리</t>
+          <t>공정별 데이터 실시간 수집·분석 — 작업장/기계종류/작업인원/필요스킬등급/작업시간/조립공정/전·후공정 DB</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>ERP-027</t>
+          <t>ERP-026</t>
         </is>
       </c>
       <c r="C148" s="16" t="inlineStr">
@@ -6074,12 +6074,12 @@
       </c>
       <c r="D148" s="6" t="inlineStr">
         <is>
-          <t>품질 관리</t>
+          <t>자재흐름·물류 관리</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
         <is>
-          <t>제품 검수, 하자 관리</t>
+          <t>물류 창고, 물류 방식 관리</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>ERP-028</t>
+          <t>ERP-027</t>
         </is>
       </c>
       <c r="C149" s="16" t="inlineStr">
@@ -6109,12 +6109,12 @@
       </c>
       <c r="D149" s="6" t="inlineStr">
         <is>
-          <t>원가 DB 관리</t>
+          <t>품질 관리</t>
         </is>
       </c>
       <c r="E149" s="6" t="inlineStr">
         <is>
-          <t>자재 단가 DB, 인건비 DB, 공정비용 DB 유지</t>
+          <t>제품 검수, 하자 관리</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>ERP-029</t>
+          <t>ERP-028</t>
         </is>
       </c>
       <c r="C150" s="16" t="inlineStr">
@@ -6144,12 +6144,12 @@
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>불량·대체자재 관리</t>
+          <t>원가 DB 관리</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
         <is>
-          <t>불량품·폐품 처리, 자재 표준화·단순화, 대체 자재 연구·적용</t>
+          <t>자재 단가 DB, 인건비 DB, 공정비용 DB 유지</t>
         </is>
       </c>
       <c r="F150" s="5" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>ERP-030</t>
+          <t>ERP-029</t>
         </is>
       </c>
       <c r="C151" s="16" t="inlineStr">
@@ -6179,12 +6179,12 @@
       </c>
       <c r="D151" s="6" t="inlineStr">
         <is>
-          <t>외주 제조 관리</t>
+          <t>불량·대체자재 관리</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
-          <t>3rd party 제조업체 — 제조 의뢰, 재작업 요청, 인증서 발급</t>
+          <t>불량품·폐품 처리, 자재 표준화·단순화, 대체 자재 연구·적용</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
@@ -6204,22 +6204,22 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>DUCT-001</t>
-        </is>
-      </c>
-      <c r="C152" s="17" t="inlineStr">
-        <is>
-          <t>DUCT 건축 설비 설계</t>
+          <t>ERP-030</t>
+        </is>
+      </c>
+      <c r="C152" s="16" t="inlineStr">
+        <is>
+          <t>ERP ERP 업무</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
-          <t>건축도면 학습</t>
+          <t>외주 제조 관리</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
         <is>
-          <t>건축도(램프·빔·소방구역·실 구획) AI 판독 — 설치 불가 지역 구분</t>
+          <t>3rd party 제조업체 — 제조 의뢰, 재작업 요청, 인증서 발급</t>
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>DUCT-002</t>
+          <t>DUCT-001</t>
         </is>
       </c>
       <c r="C153" s="17" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="D153" s="6" t="inlineStr">
         <is>
-          <t>건축 도면 호출</t>
+          <t>건축도면 학습</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr">
         <is>
-          <t>층별·대공간 복수 도면 호출, 연결 Point(XYZ) 탐색</t>
+          <t>건축도(램프·빔·소방구역·실 구획) AI 판독 — 설치 불가 지역 구분</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>DUCT-003</t>
+          <t>DUCT-002</t>
         </is>
       </c>
       <c r="C154" s="17" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="D154" s="6" t="inlineStr">
         <is>
-          <t>Duct 자재 DB</t>
+          <t>건축 도면 호출</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
         <is>
-          <t>Duct 종류/손실/무게/Size별 최대길이, Pitting/Hanger/Joint/Insulation, 최대 Sizing·블록화 설계(수동변경·분할합체), 실 용도별 설계기준(풍속), 장비 기초 도면</t>
+          <t>층별·대공간 복수 도면 호출, 연결 Point(XYZ) 탐색</t>
         </is>
       </c>
       <c r="F154" s="5" t="inlineStr">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>DUCT-004</t>
+          <t>DUCT-003</t>
         </is>
       </c>
       <c r="C155" s="17" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="D155" s="6" t="inlineStr">
         <is>
-          <t>설비 설계 조건 설정</t>
+          <t>Duct 자재 DB</t>
         </is>
       </c>
       <c r="E155" s="6" t="inlineStr">
         <is>
-          <t>풍량 계산(실별 용도·환기횟수/국소 급배기/임의입력), 장비 리스트 풍량, 건축 정보(층고·보·텍스높이·마감), 용도(급기/배기/순환/국부), 입출구 Point, Diffuser 기준, 출발-종착점(장비↔실 Combo 연결), 공기 조건(GasType·온도·습도·밀도), Point별 유속(Size)/Std 기준, Duct Option(점검구·Turning)</t>
+          <t>Duct 종류/손실/무게/Size별 최대길이, Pitting/Hanger/Joint/Insulation, 최대 Sizing·블록화 설계(수동변경·분할합체), 실 용도별 설계기준(풍속), 장비 기초 도면</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>DUCT-005</t>
+          <t>DUCT-004</t>
         </is>
       </c>
       <c r="C156" s="17" t="inlineStr">
@@ -6354,12 +6354,12 @@
       </c>
       <c r="D156" s="6" t="inlineStr">
         <is>
-          <t>Duct 자동 배치</t>
+          <t>설비 설계 조건 설정</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr">
         <is>
-          <t>가장 빠른 길 찾기(유체 흐름 고려 설계), Diffuser 자동 배치(위치·수량 조정), 수동 조정(Drag·Click)</t>
+          <t>풍량 계산(실별 용도·환기횟수/국소 급배기/임의입력), 장비 리스트 풍량, 건축 정보(층고·보·텍스높이·마감), 용도(급기/배기/순환/국부), 입출구 Point, Diffuser 기준, 출발-종착점(장비↔실 Combo 연결), 공기 조건(GasType·온도·습도·밀도), Point별 유속(Size)/Std 기준, Duct Option(점검구·Turning)</t>
         </is>
       </c>
       <c r="F156" s="5" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>DUCT-006</t>
+          <t>DUCT-005</t>
         </is>
       </c>
       <c r="C157" s="17" t="inlineStr">
@@ -6389,12 +6389,12 @@
       </c>
       <c r="D157" s="6" t="inlineStr">
         <is>
-          <t>설비 기술자료 계산</t>
+          <t>Duct 자동 배치</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr">
         <is>
-          <t>압력 손실/Leak율/온도 변화/결로/하중 계산, 장비 풍량 vs 설계 풍량 비교, 냉난방·배기 자료 기반 장비 선정</t>
+          <t>가장 빠른 길 찾기(유체 흐름 고려 설계), Diffuser 자동 배치(위치·수량 조정), 수동 조정(Drag·Click)</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>DUCT-007</t>
+          <t>DUCT-006</t>
         </is>
       </c>
       <c r="C158" s="17" t="inlineStr">
@@ -6424,12 +6424,12 @@
       </c>
       <c r="D158" s="6" t="inlineStr">
         <is>
-          <t>설비-EDIM 연결</t>
+          <t>설비 기술자료 계산</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
         <is>
-          <t>설계 결과의 EDIM 연동 — 기술(BOM/Code), 제조(최소 스크랩), 자재(구매), 영업(견적)</t>
+          <t>압력 손실/Leak율/온도 변화/결로/하중 계산, 장비 풍량 vs 설계 풍량 비교, 냉난방·배기 자료 기반 장비 선정</t>
         </is>
       </c>
       <c r="F158" s="5" t="inlineStr">
@@ -6449,22 +6449,22 @@
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>AI-001</t>
-        </is>
-      </c>
-      <c r="C159" s="18" t="inlineStr">
-        <is>
-          <t>AI AI 기능</t>
+          <t>DUCT-007</t>
+        </is>
+      </c>
+      <c r="C159" s="17" t="inlineStr">
+        <is>
+          <t>DUCT 건축 설비 설계</t>
         </is>
       </c>
       <c r="D159" s="6" t="inlineStr">
         <is>
-          <t>도면 학습 파이프라인</t>
+          <t>설비-EDIM 연결</t>
         </is>
       </c>
       <c r="E159" s="6" t="inlineStr">
         <is>
-          <t>CAD 변환→추출→구조화→RAG 인덱싱 잡 관리</t>
+          <t>설계 결과의 EDIM 연동 — 기술(BOM/Code), 제조(최소 스크랩), 자재(구매), 영업(견적)</t>
         </is>
       </c>
       <c r="F159" s="5" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>AI-002</t>
+          <t>AI-001</t>
         </is>
       </c>
       <c r="C160" s="18" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
-          <t>메타데이터 추출</t>
+          <t>도면 학습 파이프라인</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
         <is>
-          <t>타이틀블록(도번·Rev·재질·축척)·레이어·블록 속성·BOM 규칙 분류</t>
+          <t>CAD 변환→추출→구조화→RAG 인덱싱 잡 관리</t>
         </is>
       </c>
       <c r="F160" s="5" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>AI-003</t>
+          <t>AI-002</t>
         </is>
       </c>
       <c r="C161" s="18" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="D161" s="6" t="inlineStr">
         <is>
-          <t>2D 엔티티 파싱·OCR</t>
+          <t>메타데이터 추출</t>
         </is>
       </c>
       <c r="E161" s="6" t="inlineStr">
         <is>
-          <t>DWG/DXF 엔티티(치수·공차·기호) 추출, 스캔 도면 OCR+도면인식</t>
+          <t>타이틀블록(도번·Rev·재질·축척)·레이어·블록 속성·BOM 규칙 분류</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>AI-004</t>
+          <t>AI-003</t>
         </is>
       </c>
       <c r="C162" s="18" t="inlineStr">
@@ -6564,17 +6564,17 @@
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>Macro 자동 생성</t>
+          <t>2D 엔티티 파싱·OCR</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
         <is>
-          <t>Prompt→Macro/Flowchart/Description/Coding 생성</t>
+          <t>DWG/DXF 엔티티(치수·공차·기호) 추출, 스캔 도면 OCR+도면인식</t>
         </is>
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="G162" s="5" t="inlineStr"/>
@@ -6589,7 +6589,7 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>AI-005</t>
+          <t>AI-004</t>
         </is>
       </c>
       <c r="C163" s="18" t="inlineStr">
@@ -6599,12 +6599,12 @@
       </c>
       <c r="D163" s="6" t="inlineStr">
         <is>
-          <t>4-Way 상호 변환</t>
+          <t>Macro 자동 생성</t>
         </is>
       </c>
       <c r="E163" s="6" t="inlineStr">
         <is>
-          <t>표현 간(Macro↔Flowchart 등) AI 변환</t>
+          <t>Prompt→Macro/Flowchart/Description/Coding 생성</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>AI-006</t>
+          <t>AI-005</t>
         </is>
       </c>
       <c r="C164" s="18" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
-          <t>UI 자동 제안</t>
+          <t>4-Way 상호 변환</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
         <is>
-          <t>설명→용도/항목/필요 DB Table→UI Form 초안</t>
+          <t>표현 간(Macro↔Flowchart 등) AI 변환</t>
         </is>
       </c>
       <c r="F164" s="5" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>AI-007</t>
+          <t>AI-006</t>
         </is>
       </c>
       <c r="C165" s="18" t="inlineStr">
@@ -6669,17 +6669,17 @@
       </c>
       <c r="D165" s="6" t="inlineStr">
         <is>
-          <t>사내 자료 챗봇</t>
+          <t>UI 자동 제안</t>
         </is>
       </c>
       <c r="E165" s="6" t="inlineStr">
         <is>
-          <t>도면·기술자료·서류 RAG Q&amp;A, ERP 연동 서류 생성 지원</t>
+          <t>설명→용도/항목/필요 DB Table→UI Form 초안</t>
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr"/>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>AI-008</t>
+          <t>AI-007</t>
         </is>
       </c>
       <c r="C166" s="18" t="inlineStr">
@@ -6704,17 +6704,17 @@
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>AI 생성물 승인 게이트</t>
+          <t>사내 자료 챗봇</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
         <is>
-          <t>AI 생성 Macro/UI/자료의 검토·승인 절차 강제</t>
+          <t>도면·기술자료·서류 RAG Q&amp;A, ERP 연동 서류 생성 지원</t>
         </is>
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr"/>
@@ -6729,27 +6729,27 @@
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>APP-001</t>
-        </is>
-      </c>
-      <c r="C167" s="19" t="inlineStr">
-        <is>
-          <t>APP 모바일 App</t>
+          <t>AI-008</t>
+        </is>
+      </c>
+      <c r="C167" s="18" t="inlineStr">
+        <is>
+          <t>AI AI 기능</t>
         </is>
       </c>
       <c r="D167" s="6" t="inlineStr">
         <is>
-          <t>QR 정보 열람</t>
+          <t>AI 생성물 승인 게이트</t>
         </is>
       </c>
       <c r="E167" s="6" t="inlineStr">
         <is>
-          <t>QR 스캔→도면/서류/Project History/처리할 업무</t>
+          <t>AI 생성 Macro/UI/자료의 검토·승인 절차 강제</t>
         </is>
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr"/>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>APP-002</t>
+          <t>APP-001</t>
         </is>
       </c>
       <c r="C168" s="19" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="D168" s="6" t="inlineStr">
         <is>
-          <t>모바일 승인</t>
+          <t>QR 정보 열람</t>
         </is>
       </c>
       <c r="E168" s="6" t="inlineStr">
         <is>
-          <t>업무 승인 처리(승인함·결재)</t>
+          <t>QR 스캔→도면/서류/Project History/처리할 업무</t>
         </is>
       </c>
       <c r="F168" s="5" t="inlineStr">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>APP-003</t>
+          <t>APP-002</t>
         </is>
       </c>
       <c r="C169" s="19" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="D169" s="6" t="inlineStr">
         <is>
-          <t>Project 소통</t>
+          <t>모바일 승인</t>
         </is>
       </c>
       <c r="E169" s="6" t="inlineStr">
         <is>
-          <t>Project 중심 대화, History 관리</t>
+          <t>업무 승인 처리(승인함·결재)</t>
         </is>
       </c>
       <c r="F169" s="5" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>APP-004</t>
+          <t>APP-003</t>
         </is>
       </c>
       <c r="C170" s="19" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="D170" s="6" t="inlineStr">
         <is>
-          <t>자재 입출고</t>
+          <t>Project 소통</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
         <is>
-          <t>현장 자재 입출고 처리(MI/MO)</t>
+          <t>Project 중심 대화, History 관리</t>
         </is>
       </c>
       <c r="F170" s="5" t="inlineStr">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>APP-005</t>
+          <t>APP-004</t>
         </is>
       </c>
       <c r="C171" s="19" t="inlineStr">
@@ -6879,12 +6879,12 @@
       </c>
       <c r="D171" s="6" t="inlineStr">
         <is>
-          <t>검수</t>
+          <t>자재 입출고</t>
         </is>
       </c>
       <c r="E171" s="6" t="inlineStr">
         <is>
-          <t>자재·완성품·설치완료 검수 처리</t>
+          <t>현장 자재 입출고 처리(MI/MO)</t>
         </is>
       </c>
       <c r="F171" s="5" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>APP-006</t>
+          <t>APP-005</t>
         </is>
       </c>
       <c r="C172" s="19" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>유지보수</t>
+          <t>검수</t>
         </is>
       </c>
       <c r="E172" s="6" t="inlineStr">
         <is>
-          <t>Client 유지보수 접수·처리</t>
+          <t>자재·완성품·설치완료 검수 처리</t>
         </is>
       </c>
       <c r="F172" s="5" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>APP-007</t>
+          <t>APP-006</t>
         </is>
       </c>
       <c r="C173" s="19" t="inlineStr">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="D173" s="6" t="inlineStr">
         <is>
-          <t>공지·푸시</t>
+          <t>유지보수</t>
         </is>
       </c>
       <c r="E173" s="6" t="inlineStr">
         <is>
-          <t>공지(알림) 수신, 푸시 알림</t>
+          <t>Client 유지보수 접수·처리</t>
         </is>
       </c>
       <c r="F173" s="5" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>APP-008</t>
+          <t>APP-007</t>
         </is>
       </c>
       <c r="C174" s="19" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>AR 뷰</t>
+          <t>공지·푸시</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
         <is>
-          <t>증강현실 — 3D 모델·Digital Twin 데이터 오버레이</t>
+          <t>공지(알림) 수신, 푸시 알림</t>
         </is>
       </c>
       <c r="F174" s="5" t="inlineStr">
@@ -7009,27 +7009,27 @@
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>ADM-001</t>
-        </is>
-      </c>
-      <c r="C175" s="20" t="inlineStr">
-        <is>
-          <t>ADM 관리 콘솔</t>
+          <t>APP-008</t>
+        </is>
+      </c>
+      <c r="C175" s="19" t="inlineStr">
+        <is>
+          <t>APP 모바일 App</t>
         </is>
       </c>
       <c r="D175" s="6" t="inlineStr">
         <is>
-          <t>테넌트 관리</t>
+          <t>AR 뷰</t>
         </is>
       </c>
       <c r="E175" s="6" t="inlineStr">
         <is>
-          <t>테넌트 생성·설정·상태, 요금제(SaaS)</t>
+          <t>증강현실 — 3D 모델·Digital Twin 데이터 오버레이</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>ADM-002</t>
+          <t>ADM-001</t>
         </is>
       </c>
       <c r="C176" s="20" t="inlineStr">
@@ -7054,17 +7054,17 @@
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>사용자·권한 관리 UI</t>
+          <t>테넌트 관리</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
         <is>
-          <t>SYS-003~005의 관리 화면</t>
+          <t>테넌트 생성·설정·상태, 요금제(SaaS)</t>
         </is>
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="G176" s="5" t="inlineStr"/>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>ADM-003</t>
+          <t>ADM-002</t>
         </is>
       </c>
       <c r="C177" s="20" t="inlineStr">
@@ -7089,17 +7089,17 @@
       </c>
       <c r="D177" s="6" t="inlineStr">
         <is>
-          <t>승인 관리</t>
+          <t>사용자·권한 관리 UI</t>
         </is>
       </c>
       <c r="E177" s="6" t="inlineStr">
         <is>
-          <t>승인 요청 일괄 처리·위임·규칙</t>
+          <t>SYS-003~005의 관리 화면</t>
         </is>
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr"/>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>ADM-004</t>
+          <t>ADM-003</t>
         </is>
       </c>
       <c r="C178" s="20" t="inlineStr">
@@ -7124,17 +7124,17 @@
       </c>
       <c r="D178" s="6" t="inlineStr">
         <is>
-          <t>AI 학습 관리</t>
+          <t>승인 관리</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
         <is>
-          <t>학습 데이터 등록, 파이프라인 실행·품질 확인</t>
+          <t>승인 요청 일괄 처리·위임·규칙</t>
         </is>
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G178" s="5" t="inlineStr"/>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>ADM-005</t>
+          <t>ADM-004</t>
         </is>
       </c>
       <c r="C179" s="20" t="inlineStr">
@@ -7159,17 +7159,17 @@
       </c>
       <c r="D179" s="6" t="inlineStr">
         <is>
-          <t>감사·사용량</t>
+          <t>AI 학습 관리</t>
         </is>
       </c>
       <c r="E179" s="6" t="inlineStr">
         <is>
-          <t>감사 로그, API 사용량, AI 토큰 비용 조회</t>
+          <t>학습 데이터 등록, 파이프라인 실행·품질 확인</t>
         </is>
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr"/>
@@ -7178,8 +7178,43 @@
       <c r="J179" s="5" t="inlineStr"/>
       <c r="K179" s="6" t="inlineStr"/>
     </row>
+    <row r="180">
+      <c r="A180" s="5" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="5" t="inlineStr">
+        <is>
+          <t>ADM-005</t>
+        </is>
+      </c>
+      <c r="C180" s="20" t="inlineStr">
+        <is>
+          <t>ADM 관리 콘솔</t>
+        </is>
+      </c>
+      <c r="D180" s="6" t="inlineStr">
+        <is>
+          <t>감사·사용량</t>
+        </is>
+      </c>
+      <c r="E180" s="6" t="inlineStr">
+        <is>
+          <t>감사 로그, API 사용량, AI 토큰 비용 조회</t>
+        </is>
+      </c>
+      <c r="F180" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="G180" s="5" t="inlineStr"/>
+      <c r="H180" s="5" t="inlineStr"/>
+      <c r="I180" s="6" t="inlineStr"/>
+      <c r="J180" s="5" t="inlineStr"/>
+      <c r="K180" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K179"/>
+  <autoFilter ref="A1:K180"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7693,12 +7728,12 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>다국어</t>
+          <t>다국어 (i18n)</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>영어 1차 (협의)</t>
+          <t>4개 로케일(ko/en/ja/zh) 전환 100%</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr"/>
@@ -8057,7 +8092,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>총 178건 — P (  ) · F (  ) · C (  ) · N/A (  )</t>
+          <t>총 179건 — P (  ) · F (  ) · C (  ) · N/A (  )</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/03_기능확인서_FVT/EDIM_기능확인서.xlsx
+++ b/edim-ai-blueprint/docs/03_기능확인서_FVT/EDIM_기능확인서.xlsx
@@ -720,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>PostgreSQL 16 — 스키마 53테이블 (ddl/edim_schema.sql)</t>
+          <t>PostgreSQL 16 — base 53테이블 + alembic 증분 (2026-07-25 현재 108테이블, /system/status 로 확인)</t>
         </is>
       </c>
     </row>
@@ -861,6 +861,40 @@
       <c r="C8" s="6" t="inlineStr">
         <is>
           <t>이행 데이터 또는 표준 샘플 (KDCR 3-13 코드 체계 — verify_runtime.sql 준용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>검수 근거</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>자동 검증 자산</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>라이브 스위트 115종(tests/live_all.py) · 유닛 63케이스(backend/tests, CI) · 시연 8단계(live_demo_scenario) · 성능 실측(load_baseline) — 항목별 수기 확인의 보조 근거로 첨부 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>검수 근거</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>재현 방법</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>PYTHONUTF8=1 py tests/live_all.py (전 스위트) · 개별 스위트는 tests/README.md 매핑표 참조</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/03_기능확인서_FVT/EDIM_기능확인서.xlsx
+++ b/edim-ai-blueprint/docs/03_기능확인서_FVT/EDIM_기능확인서.xlsx
@@ -1073,7 +1073,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>사용자 등록/수정/상태 변경(ACTIVE/LOCKED/RETIRED)</t>
+          <t>사용자 등록/수정/상태 변경(ACTIVE/LOCKED/RETIRED) · 관리자 비밀번호 재설정(임시 발급·잠금 동시 해제) · 마지막 관리자 강등·비활성·삭제 차단</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -1085,7 +1085,11 @@
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="6" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="6" t="inlineStr"/>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>라이브 자동검증 — SYS-003: live_password_recovery 23케이스 / SYS-007: live_u18_node_copy 17케이스</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -1213,7 +1217,7 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>노드 생성/편집/삭제 (승인 후 반영)</t>
+          <t>노드 생성/편집/삭제 (승인 후 반영) · 구조 복제(서브트리 복사 — 복제본 전부 DRAFT·300노드 상한 초과 시 거부)</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -1225,7 +1229,11 @@
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="6" t="inlineStr"/>
       <c r="J8" s="5" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>라이브 자동검증 — SYS-003: live_password_recovery 23케이스 / SYS-007: live_u18_node_copy 17케이스</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">

--- a/edim-ai-blueprint/docs/03_기능확인서_FVT/EDIM_기능확인서.xlsx
+++ b/edim-ai-blueprint/docs/03_기능확인서_FVT/EDIM_기능확인서.xlsx
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>Product Tree에서 제품 선택, Selection 시작</t>
+          <t>Product Tree에서 제품 선택, Selection 시작 · 승인된 제품만 콤보 제시(미승인·부재 시 경고)</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
@@ -4138,7 +4138,11 @@
       <c r="H91" s="5" t="inlineStr"/>
       <c r="I91" s="6" t="inlineStr"/>
       <c r="J91" s="5" t="inlineStr"/>
-      <c r="K91" s="6" t="inlineStr"/>
+      <c r="K91" s="6" t="inlineStr">
+        <is>
+          <t>라이브 자동검증 — live_cpq_product_pick 11케이스(콤보 채움·제품 전환·제목 반영)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="n">

--- a/edim-ai-blueprint/docs/03_기능확인서_FVT/EDIM_기능확인서.xlsx
+++ b/edim-ai-blueprint/docs/03_기능확인서_FVT/EDIM_기능확인서.xlsx
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>문서별 Progress(Person/date/Released Status/Approver/App.Date/Version/DOC No.) 관리</t>
+          <t>문서별 Progress(Person/date/Released Status/Approver/App.Date/Version/DOC No.) 관리 · 개정 Version 자동 증가(소수부 +1, 이전 버전 이력 보존)</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -1758,7 +1758,11 @@
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="6" t="inlineStr"/>
       <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="6" t="inlineStr"/>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>라이브 자동검증 — live_doc_revision 17케이스(개정·이력 2건·상태 규칙·형식 불가 422)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">

--- a/edim-ai-blueprint/docs/03_기능확인서_FVT/EDIM_기능확인서.xlsx
+++ b/edim-ai-blueprint/docs/03_기능확인서_FVT/EDIM_기능확인서.xlsx
@@ -7179,7 +7179,7 @@
       </c>
       <c r="E178" s="6" t="inlineStr">
         <is>
-          <t>승인 요청 일괄 처리·위임·규칙</t>
+          <t>승인 요청 일괄 처리·위임(지정/해제·권한 레벨 검사·알림)·정책 규칙(요청자 본인 결정 금지)</t>
         </is>
       </c>
       <c r="F178" s="5" t="inlineStr">
@@ -7191,7 +7191,11 @@
       <c r="H178" s="5" t="inlineStr"/>
       <c r="I178" s="6" t="inlineStr"/>
       <c r="J178" s="5" t="inlineStr"/>
-      <c r="K178" s="6" t="inlineStr"/>
+      <c r="K178" s="6" t="inlineStr">
+        <is>
+          <t>라이브 자동검증 — live_approval_delegate 22케이스 / live_approval_policy 18케이스</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="n">

--- a/edim-ai-blueprint/docs/03_기능확인서_FVT/EDIM_기능확인서.xlsx
+++ b/edim-ai-blueprint/docs/03_기능확인서_FVT/EDIM_기능확인서.xlsx
@@ -7581,10 +7581,18 @@
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>역할·레벨 + 동사(APPROVE/DEPLOY) 이중 통제 · 요청자 본인 승인 금지 정책(기본 꺼짐) · 마스킹 우회 차단</t>
+        </is>
+      </c>
       <c r="H9" s="6" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>라이브 자동검증 — live_audit_trail 21 / live_approval_policy 18 / live_password_recovery 29</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
@@ -7641,10 +7649,18 @@
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>업무 쓰기 이력 기록 — 커버리지 게이트로 미기록 증가 차단(현재 예외 18건, 위험 순 축소 중). 승인 결정자·데이터 테이블 before/after 보존</t>
+        </is>
+      </c>
       <c r="H11" s="6" t="inlineStr"/>
       <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>라이브 자동검증 — live_audit_trail 21 / live_approval_policy 18 / live_password_recovery 29</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
@@ -7671,10 +7687,18 @@
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>비밀번호 PBKDF2-HMAC-SHA256 260k+계정별 솔트(구형식 로그인 시 자동 승격) · 5회 실패 자동 잠금 · 관리자 재설정(잠금 동시 해제) · 마지막 관리자 보호</t>
+        </is>
+      </c>
       <c r="H12" s="6" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>라이브 자동검증 — live_audit_trail 21 / live_approval_policy 18 / live_password_recovery 29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">

--- a/edim-ai-blueprint/docs/03_기능확인서_FVT/EDIM_기능확인서.xlsx
+++ b/edim-ai-blueprint/docs/03_기능확인서_FVT/EDIM_기능확인서.xlsx
@@ -7651,7 +7651,7 @@
       <c r="F11" s="5" t="inlineStr"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>업무 쓰기 이력 기록 — 커버리지 게이트로 미기록 증가 차단(현재 예외 18건, 위험 순 축소 중). 승인 결정자·데이터 테이블 before/after 보존</t>
+          <t>업무 쓰기 이력 기록 — 커버리지 게이트로 미기록 증가 차단(32→9, 잔여 9건은 배치·도형·UI 정의 저장). 승인 결정자·Run 실행자·데이터 테이블 before/after·삭제 원본 보존</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr"/>

--- a/edim-ai-blueprint/docs/03_기능확인서_FVT/EDIM_기능확인서.xlsx
+++ b/edim-ai-blueprint/docs/03_기능확인서_FVT/EDIM_기능확인서.xlsx
@@ -7651,7 +7651,7 @@
       <c r="F11" s="5" t="inlineStr"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>업무 쓰기 이력 기록 — 커버리지 게이트로 미기록 증가 차단(32→9, 잔여 9건은 배치·도형·UI 정의 저장). 승인 결정자·Run 실행자·데이터 테이블 before/after·삭제 원본 보존</t>
+          <t>업무 쓰기 이력 기록 — 커버리지 게이트로 미기록 증가 차단(32→7). 승인 결정자·Run 실행자·데이터 테이블 before/after·삭제 원본·CAD 덮어쓰기 구분 보존</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr"/>
